--- a/data_out/country_spreadsheets/Austria.xlsx
+++ b/data_out/country_spreadsheets/Austria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>3.95</v>
       </c>
+      <c r="X2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>146.64</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>8.17</v>
       </c>
+      <c r="X3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>169.91</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>10.06</v>
       </c>
+      <c r="X4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>66.39</v>
       </c>
+      <c r="X5" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>153.08</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>66.39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>68.89</v>
       </c>
+      <c r="X6" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>151.95</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>68.89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>28.88</v>
       </c>
+      <c r="X7" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>28.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>26.08</v>
       </c>
+      <c r="X8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>147.68</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>113.44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>109.61</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>3.47</v>
       </c>
+      <c r="X9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>213.12</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>78.66</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>15.83</v>
       </c>
+      <c r="X10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>119.11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>15.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>25.47</v>
       </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85.38</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>109.86</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>156.26</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>25.47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>42.46</v>
       </c>
+      <c r="X12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>134.97</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>152.37</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>69.06999999999999</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>42.46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>112.23</v>
       </c>
+      <c r="X13" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>84.97</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>112.23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>41.44</v>
       </c>
+      <c r="X14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>80.04000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.44</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>122.53</v>
       </c>
+      <c r="X15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>53.26</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>122.53</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>130.21</v>
       </c>
+      <c r="X16" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>105.21</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>114.51</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>154.77</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>207.99</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>130.21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>47.47</v>
       </c>
+      <c r="X17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>124.78</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>154.22</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>47.47</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>73.84</v>
       </c>
+      <c r="X18" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>125.12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>118.11</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>126.08</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>73.84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>74.42</v>
       </c>
+      <c r="X19" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>107.66</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>74.42</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>117.99</v>
       </c>
+      <c r="X20" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>170.93</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>117.99</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>44.87</v>
       </c>
+      <c r="X21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>44.87</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>158.48</v>
       </c>
+      <c r="X22" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>215.56</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>163.18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>158.48</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>97.14</v>
       </c>
+      <c r="X23" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>82.63</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>157.56</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>223.67</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>159.95</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>97.14</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>69.43000000000001</v>
       </c>
+      <c r="X24" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>145.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>132.82</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>69.43000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>83.43000000000001</v>
       </c>
+      <c r="X25" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>160.02</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>217.19</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>161.77</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>83.43000000000001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>172.98</v>
       </c>
+      <c r="X26" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>154.43</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>228.27</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>190.21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>172.98</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>48.78</v>
       </c>
+      <c r="X27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>48.78</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>47.01</v>
       </c>
+      <c r="X28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>67.28</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>47.01</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>152.96</v>
       </c>
+      <c r="X29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>146.34</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>196.38</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>152.96</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>53.07</v>
       </c>
+      <c r="X30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>45.17</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>53.07</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>65.52</v>
       </c>
+      <c r="X31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>65.52</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>27.38</v>
       </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>27.38</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>19.62</v>
       </c>
+      <c r="X33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19.62</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>45.98</v>
       </c>
+      <c r="X34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>118.64</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>45.98</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>53.19</v>
       </c>
+      <c r="X35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>128.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>46.23</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>53.19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3237,6 +5056,57 @@
         <v>14.5</v>
       </c>
       <c r="W36" t="n">
+        <v>115.84</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>211.53</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>113.72</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN36" t="n">
         <v>115.84</v>
       </c>
     </row>
